--- a/data/trans_orig/IP1013-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>248979</t>
+          <t>248340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>250390</t>
+          <t>250392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501268</t>
+          <t>501815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506338</t>
+          <t>506340</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>676593</t>
+          <t>677199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>719324</t>
+          <t>718659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397984</t>
+          <t>1398516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229928</t>
+          <t>229474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497274</t>
+          <t>496846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>151504</t>
+          <t>151119</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309620</t>
+          <t>309430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172662</t>
+          <t>173232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177334</t>
+          <t>177342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344069</t>
+          <t>343966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>349294</t>
+          <t>348679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701128</t>
+          <t>701139</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>706269</t>
+          <t>706272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742487</t>
+          <t>742835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747517</t>
+          <t>747518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1446765</t>
+          <t>1446288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453706</t>
+          <t>1453093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>128672</t>
+          <t>128644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252272</t>
+          <t>252828</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>205383</t>
+          <t>205424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463310</t>
+          <t>464083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5998,54 +5998,54 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5993</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5306</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>699065</t>
+          <t>698378</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>704371</t>
+          <t>703774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,39 +6126,39 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443483</t>
+          <t>1443560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1013-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1013-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3778</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4865</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4381</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,5%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3364</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>253083</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>249978</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>377</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>251941</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>248340</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>248824</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,5%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>253083</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>250392</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>758</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>501815</t>
+          <t>501715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>506340</t>
+          <t>506342</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3375</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1264</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3822</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4443</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4041</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>722027</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>719325</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679757</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>677199</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>676578</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>722027</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>718659</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2101</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1398516</t>
+          <t>1398333</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1403100</t>
+          <t>1403096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4903</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4984</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4730</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>233061</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>229474</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>229573</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>706</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>496846</t>
+          <t>496592</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3715</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3703</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3975</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154173</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151119</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151131</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>447</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309430</t>
+          <t>309698</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,92 +3698,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5316</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1979</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4725</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>175978</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>172641</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177332</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>175978</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>173232</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177342</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343966</t>
+          <t>343880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348679</t>
+          <t>348672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2076</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5789</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5725</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1979</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746163</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>742841</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>747519</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1015</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704852</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>701139</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>706272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>701203</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>706268</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>746163</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>742835</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>747518</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2078</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1446288</t>
+          <t>1446498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1453093</t>
+          <t>1453716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,92 +4616,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3010</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3633</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>131057</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>128644</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>128021</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252828</t>
+          <t>252831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,92 +4959,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1477</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5093</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>209040</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>205424</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>205348</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>710</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464083</t>
+          <t>464096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5993</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6099</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>702297</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698378</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698272</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>703774</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,92%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2123</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443560</t>
+          <t>1443340</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448618</t>
+          <t>1448619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
